--- a/แผนการจัดการเรียนรู้/Course syllabus iot.xlsx
+++ b/แผนการจัดการเรียนรู้/Course syllabus iot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\embedded-system\แผนการจัดการเรียนรู้\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E42C1B-8451-4005-81DD-E3ABF80AFFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF927E6-083D-4AD1-86A7-D713519612BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="420" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1995" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -326,7 +326,7 @@
     <t>14</t>
   </si>
   <si>
-    <t xml:space="preserve">จริยธรรม AI </t>
+    <t>จริยธรรม AI ในการเขียนโปรแกรม</t>
   </si>
 </sst>
 </file>
@@ -566,7 +566,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -607,125 +607,115 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1052,277 +1042,277 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="26.25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="E2" s="43" t="s">
+      <c r="E2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="52" t="s">
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="43" t="s">
+      <c r="I2" s="23"/>
+      <c r="J2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="43"/>
-      <c r="L2" s="52" t="s">
+      <c r="K2" s="21"/>
+      <c r="L2" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="M2" s="52"/>
+      <c r="M2" s="23"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="52" t="s">
+      <c r="C3" s="21"/>
+      <c r="D3" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="52"/>
-      <c r="F3" s="43" t="s">
+      <c r="E3" s="23"/>
+      <c r="F3" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="52" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="43" t="s">
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="O3" s="43"/>
-      <c r="P3" s="55" t="s">
+      <c r="O3" s="21"/>
+      <c r="P3" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="Q3" s="55"/>
+      <c r="Q3" s="24"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="52" t="s">
+      <c r="D4" s="25"/>
+      <c r="E4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="52"/>
-      <c r="G4" s="43" t="s">
+      <c r="F4" s="23"/>
+      <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="43"/>
+      <c r="H4" s="21"/>
       <c r="I4" s="13"/>
-      <c r="J4" s="43" t="s">
+      <c r="J4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="43"/>
-      <c r="L4" s="53" t="s">
+      <c r="K4" s="21"/>
+      <c r="L4" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="53"/>
-      <c r="N4" s="43" t="s">
+      <c r="M4" s="26"/>
+      <c r="N4" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="43"/>
+      <c r="O4" s="21"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="53" t="s">
+      <c r="D5" s="25"/>
+      <c r="E5" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="53"/>
+      <c r="F5" s="26"/>
       <c r="G5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="52"/>
+      <c r="I5" s="23"/>
       <c r="J5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="52" t="s">
+      <c r="K5" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
     </row>
     <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="21"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="34"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
     </row>
     <row r="8" spans="1:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
     </row>
     <row r="9" spans="1:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
     </row>
     <row r="10" spans="1:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
       <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1346,67 +1336,67 @@
       <c r="R13" s="3"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="41"/>
     </row>
     <row r="15" spans="1:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
-      <c r="L15" s="37"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="37"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
     </row>
     <row r="16" spans="1:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
     </row>
     <row r="17" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="15" t="s">
@@ -1470,49 +1460,49 @@
       <c r="Q19" s="16"/>
     </row>
     <row r="20" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="41"/>
     </row>
     <row r="21" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="28" t="s">
         <v>69</v>
       </c>
       <c r="B22" s="42"/>
@@ -1533,25 +1523,25 @@
       <c r="Q22" s="42"/>
     </row>
     <row r="23" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="37"/>
-      <c r="Q23" s="37"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
     </row>
     <row r="24" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="11"/>
@@ -1573,415 +1563,415 @@
       <c r="Q24" s="11"/>
     </row>
     <row r="25" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39" t="s">
+      <c r="B25" s="30"/>
+      <c r="C25" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="39"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="30"/>
     </row>
     <row r="26" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="44" t="s">
+      <c r="B26" s="48"/>
+      <c r="C26" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="44"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="44"/>
-      <c r="O26" s="44"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="44"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
     </row>
     <row r="27" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="24" t="s">
+      <c r="B27" s="49"/>
+      <c r="C27" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-      <c r="N27" s="24"/>
-      <c r="O27" s="24"/>
-      <c r="P27" s="24"/>
-      <c r="Q27" s="24"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
     </row>
     <row r="28" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="24" t="s">
+      <c r="B28" s="27"/>
+      <c r="C28" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
     </row>
     <row r="29" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="24" t="s">
+      <c r="B29" s="49"/>
+      <c r="C29" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="24"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
     </row>
     <row r="30" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="24" t="s">
+      <c r="B30" s="27"/>
+      <c r="C30" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="24"/>
-      <c r="N30" s="24"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="24"/>
-      <c r="Q30" s="24"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
     </row>
     <row r="31" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="24" t="s">
+      <c r="B31" s="27"/>
+      <c r="C31" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
-      <c r="N31" s="24"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="24"/>
-      <c r="Q31" s="24"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="33" t="s">
+      <c r="A32" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="45" t="s">
+      <c r="B32" s="43"/>
+      <c r="C32" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="45"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="40" t="s">
+      <c r="A33" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="41"/>
-      <c r="C33" s="46" t="s">
+      <c r="B33" s="40"/>
+      <c r="C33" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="47"/>
-      <c r="L33" s="47"/>
-      <c r="M33" s="47"/>
-      <c r="N33" s="47"/>
-      <c r="O33" s="47"/>
-      <c r="P33" s="47"/>
-      <c r="Q33" s="48"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="P33" s="34"/>
+      <c r="Q33" s="35"/>
     </row>
     <row r="34" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="29"/>
-      <c r="C34" s="24" t="s">
+      <c r="B34" s="27"/>
+      <c r="C34" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
-      <c r="N34" s="24"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="24"/>
-      <c r="Q34" s="24"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
     </row>
     <row r="35" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="24" t="s">
+      <c r="B35" s="27"/>
+      <c r="C35" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="24"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20"/>
     </row>
     <row r="36" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="56" t="s">
+      <c r="A36" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B36" s="57"/>
-      <c r="C36" s="24" t="s">
+      <c r="B36" s="19"/>
+      <c r="C36" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
-      <c r="N36" s="24"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="24"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
     </row>
     <row r="37" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="24" t="s">
+      <c r="B37" s="27"/>
+      <c r="C37" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="24"/>
-      <c r="Q37" s="24"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20"/>
     </row>
     <row r="38" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="39" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="49" t="s">
+      <c r="A39" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="50"/>
-      <c r="C39" s="49" t="s">
+      <c r="B39" s="37"/>
+      <c r="C39" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
-      <c r="K39" s="51"/>
-      <c r="L39" s="51"/>
-      <c r="M39" s="51"/>
-      <c r="N39" s="51"/>
-      <c r="O39" s="51"/>
-      <c r="P39" s="51"/>
-      <c r="Q39" s="50"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="38"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="38"/>
+      <c r="P39" s="38"/>
+      <c r="Q39" s="37"/>
     </row>
     <row r="40" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="24" t="s">
+      <c r="B40" s="27"/>
+      <c r="C40" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24"/>
-      <c r="N40" s="24"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="24"/>
-      <c r="Q40" s="24"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
     </row>
     <row r="41" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="29" t="s">
+      <c r="A41" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="24" t="s">
+      <c r="B41" s="27"/>
+      <c r="C41" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="24"/>
-      <c r="N41" s="24"/>
-      <c r="O41" s="24"/>
-      <c r="P41" s="24"/>
-      <c r="Q41" s="24"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
     </row>
     <row r="42" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="33" t="s">
+      <c r="A42" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="33"/>
-      <c r="C42" s="45" t="s">
+      <c r="B42" s="43"/>
+      <c r="C42" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="45"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="45"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="45"/>
-      <c r="O42" s="45"/>
-      <c r="P42" s="45"/>
-      <c r="Q42" s="45"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
     </row>
     <row r="43" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="20"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="21"/>
-      <c r="N43" s="21"/>
-      <c r="O43" s="21"/>
-      <c r="P43" s="21"/>
-      <c r="Q43" s="21"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="11"/>
     </row>
     <row r="44" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="2" t="s">
@@ -1989,13 +1979,13 @@
       </c>
     </row>
     <row r="45" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
+      <c r="B45" s="50"/>
+      <c r="C45" s="50"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
       <c r="F45" s="12"/>
       <c r="G45" s="12"/>
       <c r="H45" s="12"/>
@@ -2015,19 +2005,19 @@
         <v>21</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="22" t="s">
+      <c r="D46" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="23"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="23"/>
-      <c r="L46" s="23"/>
-      <c r="M46" s="23"/>
-      <c r="N46" s="23"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="53"/>
+      <c r="M46" s="53"/>
+      <c r="N46" s="53"/>
       <c r="O46" s="5"/>
       <c r="P46" s="5" t="s">
         <v>26</v>
@@ -2042,19 +2032,19 @@
         <v>22</v>
       </c>
       <c r="C47" s="4"/>
-      <c r="D47" s="23" t="s">
+      <c r="D47" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="23"/>
-      <c r="H47" s="23"/>
-      <c r="I47" s="23"/>
-      <c r="J47" s="23"/>
-      <c r="K47" s="23"/>
-      <c r="L47" s="23"/>
-      <c r="M47" s="23"/>
-      <c r="N47" s="23"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53"/>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="53"/>
+      <c r="M47" s="53"/>
+      <c r="N47" s="53"/>
       <c r="P47" s="5" t="s">
         <v>26</v>
       </c>
@@ -2068,19 +2058,19 @@
         <v>23</v>
       </c>
       <c r="C48" s="4"/>
-      <c r="D48" s="23" t="s">
+      <c r="D48" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="E48" s="23"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="23"/>
-      <c r="H48" s="23"/>
-      <c r="I48" s="23"/>
-      <c r="J48" s="23"/>
-      <c r="K48" s="23"/>
-      <c r="L48" s="23"/>
-      <c r="M48" s="23"/>
-      <c r="N48" s="23"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="53"/>
+      <c r="N48" s="53"/>
       <c r="P48" s="5" t="s">
         <v>26</v>
       </c>
@@ -2095,19 +2085,19 @@
         <v>24</v>
       </c>
       <c r="C49" s="4"/>
-      <c r="D49" s="22" t="s">
+      <c r="D49" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="23"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="53"/>
+      <c r="M49" s="53"/>
+      <c r="N49" s="53"/>
       <c r="P49" s="5" t="s">
         <v>26</v>
       </c>
@@ -2122,19 +2112,19 @@
         <v>25</v>
       </c>
       <c r="C50" s="4"/>
-      <c r="D50" s="22" t="s">
+      <c r="D50" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="23"/>
-      <c r="J50" s="23"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="23"/>
-      <c r="M50" s="23"/>
-      <c r="N50" s="23"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="53"/>
+      <c r="M50" s="53"/>
+      <c r="N50" s="53"/>
       <c r="P50" s="5" t="s">
         <v>26</v>
       </c>
@@ -2145,78 +2135,78 @@
       <c r="T50" s="7"/>
     </row>
     <row r="51" spans="1:20" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B51" s="17" t="s">
+      <c r="B51" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="22" t="s">
+      <c r="C51" s="4"/>
+      <c r="D51" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="23"/>
-      <c r="J51" s="23"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="23"/>
-      <c r="M51" s="23"/>
-      <c r="N51" s="23"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="53"/>
+      <c r="M51" s="53"/>
+      <c r="N51" s="53"/>
       <c r="P51" s="5" t="s">
         <v>26</v>
       </c>
       <c r="Q51" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="R51" s="17"/>
+      <c r="R51" s="4"/>
       <c r="T51" s="7"/>
     </row>
     <row r="52" spans="1:20" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C52" s="17"/>
-      <c r="D52" s="22" t="s">
+      <c r="C52" s="4"/>
+      <c r="D52" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
-      <c r="J52" s="23"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="23"/>
-      <c r="M52" s="23"/>
-      <c r="N52" s="23"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53"/>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="53"/>
+      <c r="M52" s="53"/>
+      <c r="N52" s="53"/>
       <c r="P52" s="5" t="s">
         <v>26</v>
       </c>
       <c r="Q52" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="R52" s="17"/>
+      <c r="R52" s="4"/>
       <c r="T52" s="7"/>
     </row>
     <row r="53" spans="1:20" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A53" s="32" t="s">
+      <c r="A53" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B53" s="32"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="26" t="s">
+      <c r="B53" s="51"/>
+      <c r="C53" s="51"/>
+      <c r="D53" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="27"/>
-      <c r="J53" s="27"/>
-      <c r="K53" s="27"/>
-      <c r="L53" s="27"/>
-      <c r="M53" s="27"/>
-      <c r="N53" s="27"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="47"/>
+      <c r="K53" s="47"/>
+      <c r="L53" s="47"/>
+      <c r="M53" s="47"/>
+      <c r="N53" s="47"/>
       <c r="P53" s="5" t="s">
         <v>26</v>
       </c>
@@ -2231,20 +2221,20 @@
         <v>28</v>
       </c>
       <c r="B54" s="1"/>
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="25"/>
-      <c r="J54" s="25"/>
-      <c r="K54" s="25"/>
-      <c r="L54" s="25"/>
-      <c r="M54" s="25"/>
-      <c r="N54" s="25"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+      <c r="L54" s="29"/>
+      <c r="M54" s="29"/>
+      <c r="N54" s="29"/>
       <c r="O54" s="1"/>
       <c r="P54" s="5" t="s">
         <v>26</v>
@@ -2258,20 +2248,20 @@
     <row r="55" spans="1:20" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
-      <c r="C55" s="25" t="s">
+      <c r="C55" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
-      <c r="J55" s="25"/>
-      <c r="K55" s="25"/>
-      <c r="L55" s="25"/>
-      <c r="M55" s="25"/>
-      <c r="N55" s="25"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="29"/>
+      <c r="N55" s="29"/>
       <c r="O55" s="1"/>
       <c r="P55" s="5" t="s">
         <v>26</v>
@@ -2285,20 +2275,20 @@
     <row r="56" spans="1:20" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
-      <c r="C56" s="25" t="s">
+      <c r="C56" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="25"/>
-      <c r="I56" s="25"/>
-      <c r="J56" s="25"/>
-      <c r="K56" s="25"/>
-      <c r="L56" s="25"/>
-      <c r="M56" s="25"/>
-      <c r="N56" s="25"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
+      <c r="L56" s="29"/>
+      <c r="M56" s="29"/>
+      <c r="N56" s="29"/>
       <c r="O56" s="1"/>
       <c r="P56" s="5" t="s">
         <v>26</v>
@@ -2327,14 +2317,14 @@
       <c r="I57" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J57" s="25" t="s">
+      <c r="J57" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="K57" s="25"/>
-      <c r="L57" s="25"/>
-      <c r="M57" s="25"/>
-      <c r="N57" s="25"/>
-      <c r="O57" s="25"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
+      <c r="M57" s="29"/>
+      <c r="N57" s="29"/>
+      <c r="O57" s="29"/>
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
       <c r="R57" s="4"/>
@@ -2353,12 +2343,6 @@
       <c r="I58" s="10"/>
       <c r="J58" s="10"/>
       <c r="K58" s="12"/>
-      <c r="L58" s="18"/>
-      <c r="M58" s="18"/>
-      <c r="N58" s="18"/>
-      <c r="O58" s="18"/>
-      <c r="P58" s="18"/>
-      <c r="Q58" s="18"/>
       <c r="R58" s="4"/>
     </row>
     <row r="59" spans="1:20" ht="23.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2371,42 +2355,30 @@
       <c r="I59" s="9"/>
       <c r="J59" s="9"/>
       <c r="K59" s="12"/>
-      <c r="L59" s="19"/>
-      <c r="M59" s="19"/>
-      <c r="N59" s="19"/>
-      <c r="O59" s="19"/>
-      <c r="P59" s="19"/>
-      <c r="Q59" s="19"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="5"/>
       <c r="R59" s="4"/>
     </row>
     <row r="60" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="18"/>
-      <c r="I60" s="18"/>
-      <c r="J60" s="18"/>
-      <c r="L60" s="19"/>
-      <c r="M60" s="19"/>
-      <c r="N60" s="19"/>
-      <c r="O60" s="19"/>
-      <c r="P60" s="19"/>
-      <c r="Q60" s="19"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="5"/>
       <c r="R60" s="4"/>
     </row>
     <row r="61" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="E61" s="18"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="H61" s="18"/>
-      <c r="I61" s="18"/>
-      <c r="J61" s="18"/>
-      <c r="L61" s="19"/>
-      <c r="M61" s="19"/>
-      <c r="N61" s="19"/>
-      <c r="O61" s="19"/>
-      <c r="P61" s="19"/>
-      <c r="Q61" s="19"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="5"/>
       <c r="R61" s="4"/>
     </row>
     <row r="62" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2415,6 +2387,73 @@
     <row r="63" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="83">
+    <mergeCell ref="D51:N51"/>
+    <mergeCell ref="D52:N52"/>
+    <mergeCell ref="C40:Q40"/>
+    <mergeCell ref="D50:N50"/>
+    <mergeCell ref="D47:N47"/>
+    <mergeCell ref="D49:N49"/>
+    <mergeCell ref="D46:N46"/>
+    <mergeCell ref="C41:Q41"/>
+    <mergeCell ref="D48:N48"/>
+    <mergeCell ref="C56:N56"/>
+    <mergeCell ref="D53:N53"/>
+    <mergeCell ref="C54:N54"/>
+    <mergeCell ref="C55:N55"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A7:Q7"/>
+    <mergeCell ref="A14:Q14"/>
+    <mergeCell ref="A12:Q12"/>
+    <mergeCell ref="A21:Q21"/>
+    <mergeCell ref="A10:Q10"/>
+    <mergeCell ref="A9:Q9"/>
+    <mergeCell ref="A11:Q11"/>
+    <mergeCell ref="A15:Q15"/>
+    <mergeCell ref="A16:Q16"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C27:Q27"/>
+    <mergeCell ref="C29:Q29"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A20:Q20"/>
+    <mergeCell ref="A22:Q22"/>
+    <mergeCell ref="C31:Q31"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="A8:Q8"/>
+    <mergeCell ref="J57:O57"/>
+    <mergeCell ref="C25:Q25"/>
+    <mergeCell ref="C26:Q26"/>
+    <mergeCell ref="C42:Q42"/>
+    <mergeCell ref="C30:Q30"/>
+    <mergeCell ref="C32:Q32"/>
+    <mergeCell ref="C33:Q33"/>
+    <mergeCell ref="C34:Q34"/>
+    <mergeCell ref="C35:Q35"/>
+    <mergeCell ref="C37:Q37"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:Q39"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:Q36"/>
     <mergeCell ref="B3:C3"/>
@@ -2431,73 +2470,6 @@
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A6:Q6"/>
-    <mergeCell ref="A8:Q8"/>
-    <mergeCell ref="J57:O57"/>
-    <mergeCell ref="C25:Q25"/>
-    <mergeCell ref="C26:Q26"/>
-    <mergeCell ref="C42:Q42"/>
-    <mergeCell ref="C30:Q30"/>
-    <mergeCell ref="C32:Q32"/>
-    <mergeCell ref="C33:Q33"/>
-    <mergeCell ref="C34:Q34"/>
-    <mergeCell ref="C35:Q35"/>
-    <mergeCell ref="C37:Q37"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:Q39"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C27:Q27"/>
-    <mergeCell ref="C29:Q29"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A20:Q20"/>
-    <mergeCell ref="A22:Q22"/>
-    <mergeCell ref="C31:Q31"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A7:Q7"/>
-    <mergeCell ref="A14:Q14"/>
-    <mergeCell ref="A12:Q12"/>
-    <mergeCell ref="A21:Q21"/>
-    <mergeCell ref="A10:Q10"/>
-    <mergeCell ref="A9:Q9"/>
-    <mergeCell ref="A11:Q11"/>
-    <mergeCell ref="A15:Q15"/>
-    <mergeCell ref="A16:Q16"/>
-    <mergeCell ref="C56:N56"/>
-    <mergeCell ref="D53:N53"/>
-    <mergeCell ref="C54:N54"/>
-    <mergeCell ref="C55:N55"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="D51:N51"/>
-    <mergeCell ref="D52:N52"/>
-    <mergeCell ref="C40:Q40"/>
-    <mergeCell ref="D50:N50"/>
-    <mergeCell ref="D47:N47"/>
-    <mergeCell ref="D49:N49"/>
-    <mergeCell ref="D46:N46"/>
-    <mergeCell ref="C41:Q41"/>
-    <mergeCell ref="D48:N48"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
